--- a/Analysis/output/Value number raw data.xlsx
+++ b/Analysis/output/Value number raw data.xlsx
@@ -231,7 +231,7 @@
     <t xml:space="preserve">Tax-form share of Q1 minutes (W-9/W-8 season)</t>
   </si>
   <si>
-    <t xml:space="preserve">Q1 contains tax-form season → annualising Q1 overstates load (conservative)</t>
+    <t xml:space="preserve">NOT a proven peak: tax forms come with new-creator onboarding (slack L171) and Ops calls June 'tax form season again' (L201). Treat as neutral.</t>
   </si>
   <si>
     <t xml:space="preserve">Hours, 2026-01</t>
@@ -2523,7 +2523,7 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>52</v>
       </c>

--- a/Analysis/output/Value number raw data.xlsx
+++ b/Analysis/output/Value number raw data.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="488">
   <si>
     <t xml:space="preserve">Value number — support hire avoided (CFO worksheet)</t>
   </si>
@@ -195,10 +195,13 @@
     <t xml:space="preserve">Half a person still avoided</t>
   </si>
   <si>
-    <t xml:space="preserve">Worst case — FTE needed, with support automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worst case — value per year, with automation</t>
+    <t xml:space="preserve">Worst case — FTE needed, IF thumbnail swaps were also automated (not selected)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario only. The selected automation is tax forms (D1), which doesn't touch thumbnails; the headline floor is B32.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst case — value per year, IF thumbnails automated (not selected)</t>
   </si>
   <si>
     <t xml:space="preserve">Unblocker: Q2 support tickets (same columns, Apr 1 – Jun 30). Paste below row 142 on 'Tickets (raw)' and extend ranges, or rerun the builder.</t>
@@ -283,6 +286,9 @@
   </si>
   <si>
     <t xml:space="preserve">Analysis/automation/playbooks.json — share of deflected tickets still needing a person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worst case — FTE needed, IF thumbnails automated (not selected)</t>
   </si>
   <si>
     <t xml:space="preserve">Thumbnails deflected to self-serve; other work unchanged</t>
@@ -2412,7 +2418,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
         <v>41</v>
       </c>
@@ -2420,11 +2426,13 @@
         <f aca="false">'Stress tests'!B23</f>
         <v>0.255021367521368</v>
       </c>
-      <c r="C33" s="7"/>
+      <c r="C33" s="7" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" s="19" t="n">
         <f aca="false">MAX(0,B6-B33)*B23</f>
@@ -2440,7 +2448,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2470,74 +2478,74 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" s="12" t="n">
         <f aca="false">Summary!B17*2/Summary!B8</f>
         <v>0.271153846153846</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="12" t="n">
         <f aca="false">Summary!B17*3/Summary!B8</f>
         <v>0.406730769230769</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="20" t="n">
         <f aca="false">Summary!B17/Summary!B5</f>
         <v>0.135576923076923</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" s="21" t="n">
         <f aca="false">Breakdown!E4</f>
         <v>0.367612293144208</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" s="22" t="n">
         <f aca="false">Breakdown!D14</f>
@@ -2547,7 +2555,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">Breakdown!D16</f>
@@ -2557,50 +2565,50 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">B11/B10-1</f>
         <v>0.0242214532871974</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" s="12" t="n">
         <f aca="false">Summary!B18*2</f>
         <v>0.271153846153846</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B16" s="6" t="n">
         <f aca="false">Sources!$D$9</f>
         <v>47</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">Breakdown!B5/Summary!B7</f>
@@ -2610,14 +2618,14 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" s="6" t="n">
         <f aca="false">Breakdown!$B$34</f>
         <v>6</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" s="13" t="n">
         <f aca="false">B16/B18</f>
@@ -2626,7 +2634,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" s="22" t="n">
         <f aca="false">Breakdown!F5</f>
@@ -2636,7 +2644,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="12" t="n">
         <f aca="false">(Summary!B15-Breakdown!C5)/60/Summary!B7</f>
@@ -2653,46 +2661,46 @@
         <v>0.516132478632479</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B22" s="25" t="n">
         <v>0.2</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="B23" s="24" t="n">
         <f aca="false">(B16*((1-B22)*B24+B22*B19)/60+B20)/Summary!B8</f>
         <v>0.255021367521368</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="26" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="26"/>
@@ -2734,45 +2742,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2780,25 +2788,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" s="29" t="n">
         <v>46024</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G3" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H3" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I3" s="28" t="str">
         <f aca="false">TEXT(C3,"yyyy-mm")</f>
@@ -2814,25 +2822,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C4" s="29" t="n">
         <v>46024</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G4" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H4" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I4" s="28" t="str">
         <f aca="false">TEXT(C4,"yyyy-mm")</f>
@@ -2848,25 +2856,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C5" s="29" t="n">
         <v>46025</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G5" s="28" t="n">
         <v>15</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I5" s="28" t="str">
         <f aca="false">TEXT(C5,"yyyy-mm")</f>
@@ -2882,25 +2890,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" s="29" t="n">
         <v>46025</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G6" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I6" s="28" t="str">
         <f aca="false">TEXT(C6,"yyyy-mm")</f>
@@ -2916,25 +2924,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C7" s="29" t="n">
         <v>46027</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G7" s="28" t="n">
         <v>55</v>
       </c>
       <c r="H7" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I7" s="28" t="str">
         <f aca="false">TEXT(C7,"yyyy-mm")</f>
@@ -2950,25 +2958,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C8" s="29" t="n">
         <v>46027</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G8" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I8" s="28" t="str">
         <f aca="false">TEXT(C8,"yyyy-mm")</f>
@@ -2984,25 +2992,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" s="29" t="n">
         <v>46028</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G9" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I9" s="28" t="str">
         <f aca="false">TEXT(C9,"yyyy-mm")</f>
@@ -3018,25 +3026,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="29" t="n">
         <v>46028</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G10" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I10" s="28" t="str">
         <f aca="false">TEXT(C10,"yyyy-mm")</f>
@@ -3052,25 +3060,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C11" s="29" t="n">
         <v>46029</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G11" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I11" s="28" t="str">
         <f aca="false">TEXT(C11,"yyyy-mm")</f>
@@ -3086,25 +3094,25 @@
         <v>11</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C12" s="29" t="n">
         <v>46029</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G12" s="28" t="n">
         <v>10</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I12" s="28" t="str">
         <f aca="false">TEXT(C12,"yyyy-mm")</f>
@@ -3120,25 +3128,25 @@
         <v>12</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C13" s="29" t="n">
         <v>46030</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G13" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H13" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I13" s="28" t="str">
         <f aca="false">TEXT(C13,"yyyy-mm")</f>
@@ -3154,25 +3162,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C14" s="29" t="n">
         <v>46030</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G14" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H14" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I14" s="28" t="str">
         <f aca="false">TEXT(C14,"yyyy-mm")</f>
@@ -3188,23 +3196,23 @@
         <v>14</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C15" s="29" t="n">
         <v>46031</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F15" s="28"/>
       <c r="G15" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I15" s="28" t="str">
         <f aca="false">TEXT(C15,"yyyy-mm")</f>
@@ -3215,10 +3223,10 @@
         <v>2</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3226,25 +3234,25 @@
         <v>15</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C16" s="29" t="n">
         <v>46031</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G16" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I16" s="28" t="str">
         <f aca="false">TEXT(C16,"yyyy-mm")</f>
@@ -3260,25 +3268,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C17" s="29" t="n">
         <v>46034</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G17" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H17" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I17" s="28" t="str">
         <f aca="false">TEXT(C17,"yyyy-mm")</f>
@@ -3294,25 +3302,25 @@
         <v>17</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C18" s="29" t="n">
         <v>46034</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G18" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I18" s="28" t="str">
         <f aca="false">TEXT(C18,"yyyy-mm")</f>
@@ -3328,25 +3336,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C19" s="29" t="n">
         <v>46035</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G19" s="28" t="n">
         <v>40</v>
       </c>
       <c r="H19" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I19" s="28" t="str">
         <f aca="false">TEXT(C19,"yyyy-mm")</f>
@@ -3362,25 +3370,25 @@
         <v>19</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C20" s="29" t="n">
         <v>46035</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G20" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H20" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I20" s="28" t="str">
         <f aca="false">TEXT(C20,"yyyy-mm")</f>
@@ -3396,25 +3404,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C21" s="29" t="n">
         <v>46036</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G21" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H21" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I21" s="28" t="str">
         <f aca="false">TEXT(C21,"yyyy-mm")</f>
@@ -3430,25 +3438,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C22" s="29" t="n">
         <v>46036</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G22" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H22" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I22" s="28" t="str">
         <f aca="false">TEXT(C22,"yyyy-mm")</f>
@@ -3464,25 +3472,25 @@
         <v>22</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C23" s="29" t="n">
         <v>46037</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G23" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H23" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I23" s="28" t="str">
         <f aca="false">TEXT(C23,"yyyy-mm")</f>
@@ -3498,25 +3506,25 @@
         <v>23</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C24" s="29" t="n">
         <v>46037</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G24" s="28" t="n">
         <v>10</v>
       </c>
       <c r="H24" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I24" s="28" t="str">
         <f aca="false">TEXT(C24,"yyyy-mm")</f>
@@ -3532,25 +3540,25 @@
         <v>24</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C25" s="29" t="n">
         <v>46038</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G25" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I25" s="28" t="str">
         <f aca="false">TEXT(C25,"yyyy-mm")</f>
@@ -3566,25 +3574,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C26" s="29" t="n">
         <v>46038</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G26" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H26" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I26" s="28" t="str">
         <f aca="false">TEXT(C26,"yyyy-mm")</f>
@@ -3600,25 +3608,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C27" s="29" t="n">
         <v>46041</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G27" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H27" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I27" s="28" t="str">
         <f aca="false">TEXT(C27,"yyyy-mm")</f>
@@ -3634,25 +3642,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C28" s="29" t="n">
         <v>46041</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G28" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H28" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I28" s="28" t="str">
         <f aca="false">TEXT(C28,"yyyy-mm")</f>
@@ -3668,25 +3676,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C29" s="29" t="n">
         <v>46042</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G29" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H29" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I29" s="28" t="str">
         <f aca="false">TEXT(C29,"yyyy-mm")</f>
@@ -3702,25 +3710,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C30" s="29" t="n">
         <v>46042</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G30" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H30" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I30" s="28" t="str">
         <f aca="false">TEXT(C30,"yyyy-mm")</f>
@@ -3736,25 +3744,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C31" s="29" t="n">
         <v>46043</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G31" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H31" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I31" s="28" t="str">
         <f aca="false">TEXT(C31,"yyyy-mm")</f>
@@ -3770,25 +3778,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C32" s="29" t="n">
         <v>46043</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G32" s="28" t="n">
         <v>40</v>
       </c>
       <c r="H32" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I32" s="28" t="str">
         <f aca="false">TEXT(C32,"yyyy-mm")</f>
@@ -3804,25 +3812,25 @@
         <v>32</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C33" s="29" t="n">
         <v>46044</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G33" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H33" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I33" s="28" t="str">
         <f aca="false">TEXT(C33,"yyyy-mm")</f>
@@ -3838,25 +3846,25 @@
         <v>33</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C34" s="29" t="n">
         <v>46044</v>
       </c>
       <c r="D34" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G34" s="28" t="n">
         <v>10</v>
       </c>
       <c r="H34" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I34" s="28" t="str">
         <f aca="false">TEXT(C34,"yyyy-mm")</f>
@@ -3872,25 +3880,25 @@
         <v>34</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C35" s="29" t="n">
         <v>46045</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G35" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H35" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I35" s="28" t="str">
         <f aca="false">TEXT(C35,"yyyy-mm")</f>
@@ -3906,25 +3914,25 @@
         <v>35</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C36" s="29" t="n">
         <v>46045</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G36" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H36" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I36" s="28" t="str">
         <f aca="false">TEXT(C36,"yyyy-mm")</f>
@@ -3940,25 +3948,25 @@
         <v>36</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C37" s="29" t="n">
         <v>46048</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G37" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H37" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I37" s="28" t="str">
         <f aca="false">TEXT(C37,"yyyy-mm")</f>
@@ -3974,25 +3982,25 @@
         <v>37</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C38" s="29" t="n">
         <v>46048</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G38" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H38" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I38" s="28" t="str">
         <f aca="false">TEXT(C38,"yyyy-mm")</f>
@@ -4008,25 +4016,25 @@
         <v>38</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C39" s="29" t="n">
         <v>46049</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G39" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H39" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I39" s="28" t="str">
         <f aca="false">TEXT(C39,"yyyy-mm")</f>
@@ -4042,23 +4050,23 @@
         <v>39</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C40" s="29" t="n">
         <v>46049</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F40" s="28"/>
       <c r="G40" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H40" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I40" s="28" t="str">
         <f aca="false">TEXT(C40,"yyyy-mm")</f>
@@ -4069,10 +4077,10 @@
         <v>5</v>
       </c>
       <c r="K40" s="31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4080,25 +4088,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C41" s="29" t="n">
         <v>46050</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F41" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G41" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H41" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I41" s="28" t="str">
         <f aca="false">TEXT(C41,"yyyy-mm")</f>
@@ -4114,25 +4122,25 @@
         <v>41</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C42" s="29" t="n">
         <v>46050</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G42" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H42" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I42" s="28" t="str">
         <f aca="false">TEXT(C42,"yyyy-mm")</f>
@@ -4148,25 +4156,25 @@
         <v>42</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C43" s="29" t="n">
         <v>46051</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G43" s="28" t="n">
         <v>40</v>
       </c>
       <c r="H43" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I43" s="28" t="str">
         <f aca="false">TEXT(C43,"yyyy-mm")</f>
@@ -4182,25 +4190,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C44" s="29" t="n">
         <v>46051</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F44" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G44" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H44" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I44" s="28" t="str">
         <f aca="false">TEXT(C44,"yyyy-mm")</f>
@@ -4216,25 +4224,25 @@
         <v>44</v>
       </c>
       <c r="B45" s="28" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C45" s="29" t="n">
         <v>46052</v>
       </c>
       <c r="D45" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E45" s="28" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F45" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G45" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H45" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I45" s="28" t="str">
         <f aca="false">TEXT(C45,"yyyy-mm")</f>
@@ -4250,25 +4258,25 @@
         <v>45</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C46" s="29" t="n">
         <v>46052</v>
       </c>
       <c r="D46" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G46" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H46" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I46" s="28" t="str">
         <f aca="false">TEXT(C46,"yyyy-mm")</f>
@@ -4284,25 +4292,25 @@
         <v>46</v>
       </c>
       <c r="B47" s="28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C47" s="29" t="n">
         <v>46055</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G47" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H47" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I47" s="28" t="str">
         <f aca="false">TEXT(C47,"yyyy-mm")</f>
@@ -4318,25 +4326,25 @@
         <v>47</v>
       </c>
       <c r="B48" s="28" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C48" s="29" t="n">
         <v>46055</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E48" s="28" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F48" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G48" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H48" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I48" s="28" t="str">
         <f aca="false">TEXT(C48,"yyyy-mm")</f>
@@ -4352,25 +4360,25 @@
         <v>48</v>
       </c>
       <c r="B49" s="28" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C49" s="29" t="n">
         <v>46056</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E49" s="28" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F49" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G49" s="28" t="n">
         <v>10</v>
       </c>
       <c r="H49" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I49" s="28" t="str">
         <f aca="false">TEXT(C49,"yyyy-mm")</f>
@@ -4386,25 +4394,25 @@
         <v>49</v>
       </c>
       <c r="B50" s="28" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C50" s="29" t="n">
         <v>46056</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F50" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G50" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H50" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I50" s="28" t="str">
         <f aca="false">TEXT(C50,"yyyy-mm")</f>
@@ -4420,25 +4428,25 @@
         <v>50</v>
       </c>
       <c r="B51" s="28" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C51" s="29" t="n">
         <v>46057</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F51" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G51" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H51" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I51" s="28" t="str">
         <f aca="false">TEXT(C51,"yyyy-mm")</f>
@@ -4454,25 +4462,25 @@
         <v>51</v>
       </c>
       <c r="B52" s="28" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C52" s="29" t="n">
         <v>46057</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E52" s="28" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F52" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G52" s="28" t="n">
         <v>55</v>
       </c>
       <c r="H52" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I52" s="28" t="str">
         <f aca="false">TEXT(C52,"yyyy-mm")</f>
@@ -4488,25 +4496,25 @@
         <v>52</v>
       </c>
       <c r="B53" s="28" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C53" s="29" t="n">
         <v>46058</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F53" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G53" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H53" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I53" s="28" t="str">
         <f aca="false">TEXT(C53,"yyyy-mm")</f>
@@ -4522,25 +4530,25 @@
         <v>53</v>
       </c>
       <c r="B54" s="28" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C54" s="29" t="n">
         <v>46058</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E54" s="28" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F54" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G54" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H54" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I54" s="28" t="str">
         <f aca="false">TEXT(C54,"yyyy-mm")</f>
@@ -4556,25 +4564,25 @@
         <v>54</v>
       </c>
       <c r="B55" s="28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C55" s="29" t="n">
         <v>46059</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E55" s="28" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F55" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G55" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H55" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I55" s="28" t="str">
         <f aca="false">TEXT(C55,"yyyy-mm")</f>
@@ -4590,25 +4598,25 @@
         <v>55</v>
       </c>
       <c r="B56" s="28" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C56" s="29" t="n">
         <v>46059</v>
       </c>
       <c r="D56" s="28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E56" s="28" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F56" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G56" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H56" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I56" s="28" t="str">
         <f aca="false">TEXT(C56,"yyyy-mm")</f>
@@ -4624,25 +4632,25 @@
         <v>56</v>
       </c>
       <c r="B57" s="28" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C57" s="29" t="n">
         <v>46062</v>
       </c>
       <c r="D57" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F57" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G57" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H57" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I57" s="28" t="str">
         <f aca="false">TEXT(C57,"yyyy-mm")</f>
@@ -4658,25 +4666,25 @@
         <v>57</v>
       </c>
       <c r="B58" s="28" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C58" s="29" t="n">
         <v>46062</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F58" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G58" s="28" t="n">
         <v>10</v>
       </c>
       <c r="H58" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I58" s="28" t="str">
         <f aca="false">TEXT(C58,"yyyy-mm")</f>
@@ -4692,25 +4700,25 @@
         <v>58</v>
       </c>
       <c r="B59" s="28" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C59" s="29" t="n">
         <v>46063</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E59" s="28" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F59" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G59" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H59" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I59" s="28" t="str">
         <f aca="false">TEXT(C59,"yyyy-mm")</f>
@@ -4726,25 +4734,25 @@
         <v>59</v>
       </c>
       <c r="B60" s="28" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C60" s="29" t="n">
         <v>46063</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F60" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G60" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H60" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I60" s="28" t="str">
         <f aca="false">TEXT(C60,"yyyy-mm")</f>
@@ -4760,25 +4768,25 @@
         <v>60</v>
       </c>
       <c r="B61" s="28" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C61" s="29" t="n">
         <v>46064</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F61" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G61" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H61" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I61" s="28" t="str">
         <f aca="false">TEXT(C61,"yyyy-mm")</f>
@@ -4794,25 +4802,25 @@
         <v>61</v>
       </c>
       <c r="B62" s="28" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C62" s="29" t="n">
         <v>46064</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E62" s="28" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F62" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G62" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H62" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I62" s="28" t="str">
         <f aca="false">TEXT(C62,"yyyy-mm")</f>
@@ -4828,25 +4836,25 @@
         <v>62</v>
       </c>
       <c r="B63" s="28" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C63" s="29" t="n">
         <v>46065</v>
       </c>
       <c r="D63" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F63" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G63" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H63" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I63" s="28" t="str">
         <f aca="false">TEXT(C63,"yyyy-mm")</f>
@@ -4862,25 +4870,25 @@
         <v>63</v>
       </c>
       <c r="B64" s="28" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C64" s="29" t="n">
         <v>46065</v>
       </c>
       <c r="D64" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E64" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F64" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G64" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H64" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I64" s="28" t="str">
         <f aca="false">TEXT(C64,"yyyy-mm")</f>
@@ -4896,25 +4904,25 @@
         <v>64</v>
       </c>
       <c r="B65" s="28" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C65" s="29" t="n">
         <v>46066</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E65" s="28" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F65" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G65" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H65" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I65" s="28" t="str">
         <f aca="false">TEXT(C65,"yyyy-mm")</f>
@@ -4930,25 +4938,25 @@
         <v>65</v>
       </c>
       <c r="B66" s="28" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C66" s="29" t="n">
         <v>46066</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E66" s="28" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F66" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G66" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H66" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I66" s="28" t="str">
         <f aca="false">TEXT(C66,"yyyy-mm")</f>
@@ -4964,25 +4972,25 @@
         <v>66</v>
       </c>
       <c r="B67" s="28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C67" s="29" t="n">
         <v>46069</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E67" s="28" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F67" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G67" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H67" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I67" s="28" t="str">
         <f aca="false">TEXT(C67,"yyyy-mm")</f>
@@ -4998,25 +5006,25 @@
         <v>67</v>
       </c>
       <c r="B68" s="28" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C68" s="29" t="n">
         <v>46069</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F68" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G68" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H68" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I68" s="28" t="str">
         <f aca="false">TEXT(C68,"yyyy-mm")</f>
@@ -5032,25 +5040,25 @@
         <v>68</v>
       </c>
       <c r="B69" s="28" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C69" s="29" t="n">
         <v>46070</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E69" s="28" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F69" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G69" s="28" t="n">
         <v>55</v>
       </c>
       <c r="H69" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I69" s="28" t="str">
         <f aca="false">TEXT(C69,"yyyy-mm")</f>
@@ -5066,23 +5074,23 @@
         <v>69</v>
       </c>
       <c r="B70" s="30" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C70" s="29" t="n">
         <v>46070</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F70" s="28"/>
       <c r="G70" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H70" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I70" s="28" t="str">
         <f aca="false">TEXT(C70,"yyyy-mm")</f>
@@ -5093,10 +5101,10 @@
         <v>8</v>
       </c>
       <c r="K70" s="31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L70" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5104,25 +5112,25 @@
         <v>70</v>
       </c>
       <c r="B71" s="28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C71" s="29" t="n">
         <v>46071</v>
       </c>
       <c r="D71" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E71" s="28" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F71" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G71" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H71" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I71" s="28" t="str">
         <f aca="false">TEXT(C71,"yyyy-mm")</f>
@@ -5138,25 +5146,25 @@
         <v>71</v>
       </c>
       <c r="B72" s="28" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C72" s="29" t="n">
         <v>46071</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F72" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G72" s="28" t="n">
         <v>10</v>
       </c>
       <c r="H72" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I72" s="28" t="str">
         <f aca="false">TEXT(C72,"yyyy-mm")</f>
@@ -5172,25 +5180,25 @@
         <v>72</v>
       </c>
       <c r="B73" s="28" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C73" s="29" t="n">
         <v>46072</v>
       </c>
       <c r="D73" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F73" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G73" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H73" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I73" s="28" t="str">
         <f aca="false">TEXT(C73,"yyyy-mm")</f>
@@ -5206,25 +5214,25 @@
         <v>73</v>
       </c>
       <c r="B74" s="28" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C74" s="29" t="n">
         <v>46072</v>
       </c>
       <c r="D74" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E74" s="28" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F74" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G74" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H74" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I74" s="28" t="str">
         <f aca="false">TEXT(C74,"yyyy-mm")</f>
@@ -5240,25 +5248,25 @@
         <v>74</v>
       </c>
       <c r="B75" s="28" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C75" s="29" t="n">
         <v>46073</v>
       </c>
       <c r="D75" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E75" s="28" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F75" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G75" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H75" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I75" s="28" t="str">
         <f aca="false">TEXT(C75,"yyyy-mm")</f>
@@ -5274,25 +5282,25 @@
         <v>75</v>
       </c>
       <c r="B76" s="28" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C76" s="29" t="n">
         <v>46073</v>
       </c>
       <c r="D76" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F76" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G76" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H76" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I76" s="28" t="str">
         <f aca="false">TEXT(C76,"yyyy-mm")</f>
@@ -5308,25 +5316,25 @@
         <v>76</v>
       </c>
       <c r="B77" s="28" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C77" s="29" t="n">
         <v>46076</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E77" s="28" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F77" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G77" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H77" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I77" s="28" t="str">
         <f aca="false">TEXT(C77,"yyyy-mm")</f>
@@ -5342,25 +5350,25 @@
         <v>77</v>
       </c>
       <c r="B78" s="28" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C78" s="29" t="n">
         <v>46076</v>
       </c>
       <c r="D78" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E78" s="28" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F78" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G78" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H78" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I78" s="28" t="str">
         <f aca="false">TEXT(C78,"yyyy-mm")</f>
@@ -5376,25 +5384,25 @@
         <v>78</v>
       </c>
       <c r="B79" s="28" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C79" s="29" t="n">
         <v>46077</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E79" s="28" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F79" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G79" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H79" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I79" s="28" t="str">
         <f aca="false">TEXT(C79,"yyyy-mm")</f>
@@ -5410,25 +5418,25 @@
         <v>79</v>
       </c>
       <c r="B80" s="28" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C80" s="29" t="n">
         <v>46077</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E80" s="28" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F80" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G80" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H80" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I80" s="28" t="str">
         <f aca="false">TEXT(C80,"yyyy-mm")</f>
@@ -5444,25 +5452,25 @@
         <v>80</v>
       </c>
       <c r="B81" s="28" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C81" s="29" t="n">
         <v>46078</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E81" s="28" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F81" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G81" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H81" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I81" s="28" t="str">
         <f aca="false">TEXT(C81,"yyyy-mm")</f>
@@ -5478,25 +5486,25 @@
         <v>81</v>
       </c>
       <c r="B82" s="28" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C82" s="29" t="n">
         <v>46078</v>
       </c>
       <c r="D82" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F82" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G82" s="28" t="n">
         <v>10</v>
       </c>
       <c r="H82" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I82" s="28" t="str">
         <f aca="false">TEXT(C82,"yyyy-mm")</f>
@@ -5512,25 +5520,25 @@
         <v>82</v>
       </c>
       <c r="B83" s="28" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C83" s="29" t="n">
         <v>46079</v>
       </c>
       <c r="D83" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E83" s="28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F83" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G83" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H83" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I83" s="28" t="str">
         <f aca="false">TEXT(C83,"yyyy-mm")</f>
@@ -5546,25 +5554,25 @@
         <v>83</v>
       </c>
       <c r="B84" s="28" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C84" s="29" t="n">
         <v>46079</v>
       </c>
       <c r="D84" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E84" s="28" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F84" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G84" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H84" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I84" s="28" t="str">
         <f aca="false">TEXT(C84,"yyyy-mm")</f>
@@ -5580,25 +5588,25 @@
         <v>84</v>
       </c>
       <c r="B85" s="28" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C85" s="29" t="n">
         <v>46080</v>
       </c>
       <c r="D85" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E85" s="28" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F85" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G85" s="28" t="n">
         <v>55</v>
       </c>
       <c r="H85" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I85" s="28" t="str">
         <f aca="false">TEXT(C85,"yyyy-mm")</f>
@@ -5614,25 +5622,25 @@
         <v>85</v>
       </c>
       <c r="B86" s="28" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C86" s="29" t="n">
         <v>46080</v>
       </c>
       <c r="D86" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E86" s="28" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F86" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G86" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H86" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I86" s="28" t="str">
         <f aca="false">TEXT(C86,"yyyy-mm")</f>
@@ -5648,25 +5656,25 @@
         <v>86</v>
       </c>
       <c r="B87" s="28" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C87" s="29" t="n">
         <v>46083</v>
       </c>
       <c r="D87" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E87" s="28" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F87" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G87" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H87" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I87" s="28" t="str">
         <f aca="false">TEXT(C87,"yyyy-mm")</f>
@@ -5682,25 +5690,25 @@
         <v>87</v>
       </c>
       <c r="B88" s="28" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C88" s="29" t="n">
         <v>46083</v>
       </c>
       <c r="D88" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E88" s="28" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F88" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G88" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H88" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I88" s="28" t="str">
         <f aca="false">TEXT(C88,"yyyy-mm")</f>
@@ -5716,25 +5724,25 @@
         <v>88</v>
       </c>
       <c r="B89" s="28" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C89" s="29" t="n">
         <v>46084</v>
       </c>
       <c r="D89" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E89" s="28" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F89" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G89" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H89" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I89" s="28" t="str">
         <f aca="false">TEXT(C89,"yyyy-mm")</f>
@@ -5750,25 +5758,25 @@
         <v>89</v>
       </c>
       <c r="B90" s="28" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C90" s="29" t="n">
         <v>46084</v>
       </c>
       <c r="D90" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E90" s="28" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F90" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G90" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H90" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I90" s="28" t="str">
         <f aca="false">TEXT(C90,"yyyy-mm")</f>
@@ -5784,25 +5792,25 @@
         <v>90</v>
       </c>
       <c r="B91" s="28" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C91" s="29" t="n">
         <v>46085</v>
       </c>
       <c r="D91" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E91" s="28" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F91" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G91" s="28" t="n">
         <v>10</v>
       </c>
       <c r="H91" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I91" s="28" t="str">
         <f aca="false">TEXT(C91,"yyyy-mm")</f>
@@ -5818,25 +5826,25 @@
         <v>91</v>
       </c>
       <c r="B92" s="28" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C92" s="29" t="n">
         <v>46085</v>
       </c>
       <c r="D92" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E92" s="28" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F92" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G92" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H92" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I92" s="28" t="str">
         <f aca="false">TEXT(C92,"yyyy-mm")</f>
@@ -5852,25 +5860,25 @@
         <v>92</v>
       </c>
       <c r="B93" s="28" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C93" s="29" t="n">
         <v>46086</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E93" s="28" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F93" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G93" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H93" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I93" s="28" t="str">
         <f aca="false">TEXT(C93,"yyyy-mm")</f>
@@ -5886,25 +5894,25 @@
         <v>93</v>
       </c>
       <c r="B94" s="28" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C94" s="29" t="n">
         <v>46086</v>
       </c>
       <c r="D94" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E94" s="28" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F94" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G94" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H94" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I94" s="28" t="str">
         <f aca="false">TEXT(C94,"yyyy-mm")</f>
@@ -5920,25 +5928,25 @@
         <v>94</v>
       </c>
       <c r="B95" s="28" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C95" s="29" t="n">
         <v>46087</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E95" s="28" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F95" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G95" s="28" t="n">
         <v>40</v>
       </c>
       <c r="H95" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I95" s="28" t="str">
         <f aca="false">TEXT(C95,"yyyy-mm")</f>
@@ -5954,25 +5962,25 @@
         <v>95</v>
       </c>
       <c r="B96" s="28" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C96" s="29" t="n">
         <v>46087</v>
       </c>
       <c r="D96" s="28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E96" s="28" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F96" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G96" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H96" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I96" s="28" t="str">
         <f aca="false">TEXT(C96,"yyyy-mm")</f>
@@ -5988,25 +5996,25 @@
         <v>96</v>
       </c>
       <c r="B97" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C97" s="29" t="n">
         <v>46090</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E97" s="28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F97" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G97" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H97" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I97" s="28" t="str">
         <f aca="false">TEXT(C97,"yyyy-mm")</f>
@@ -6022,25 +6030,25 @@
         <v>97</v>
       </c>
       <c r="B98" s="28" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C98" s="29" t="n">
         <v>46090</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E98" s="28" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F98" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G98" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H98" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I98" s="28" t="str">
         <f aca="false">TEXT(C98,"yyyy-mm")</f>
@@ -6056,25 +6064,25 @@
         <v>98</v>
       </c>
       <c r="B99" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C99" s="29" t="n">
         <v>46091</v>
       </c>
       <c r="D99" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E99" s="28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F99" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G99" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H99" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I99" s="28" t="str">
         <f aca="false">TEXT(C99,"yyyy-mm")</f>
@@ -6090,25 +6098,25 @@
         <v>99</v>
       </c>
       <c r="B100" s="28" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C100" s="29" t="n">
         <v>46091</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E100" s="28" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F100" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G100" s="28" t="n">
         <v>10</v>
       </c>
       <c r="H100" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I100" s="28" t="str">
         <f aca="false">TEXT(C100,"yyyy-mm")</f>
@@ -6124,25 +6132,25 @@
         <v>100</v>
       </c>
       <c r="B101" s="28" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C101" s="29" t="n">
         <v>46092</v>
       </c>
       <c r="D101" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E101" s="28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F101" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G101" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H101" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I101" s="28" t="str">
         <f aca="false">TEXT(C101,"yyyy-mm")</f>
@@ -6158,23 +6166,23 @@
         <v>101</v>
       </c>
       <c r="B102" s="30" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C102" s="29" t="n">
         <v>46092</v>
       </c>
       <c r="D102" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E102" s="28" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F102" s="28"/>
       <c r="G102" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H102" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I102" s="28" t="str">
         <f aca="false">TEXT(C102,"yyyy-mm")</f>
@@ -6185,10 +6193,10 @@
         <v>11</v>
       </c>
       <c r="K102" s="31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L102" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6196,25 +6204,25 @@
         <v>102</v>
       </c>
       <c r="B103" s="28" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C103" s="29" t="n">
         <v>46093</v>
       </c>
       <c r="D103" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E103" s="28" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F103" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G103" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H103" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I103" s="28" t="str">
         <f aca="false">TEXT(C103,"yyyy-mm")</f>
@@ -6230,25 +6238,25 @@
         <v>103</v>
       </c>
       <c r="B104" s="28" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C104" s="29" t="n">
         <v>46093</v>
       </c>
       <c r="D104" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E104" s="28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F104" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G104" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H104" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I104" s="28" t="str">
         <f aca="false">TEXT(C104,"yyyy-mm")</f>
@@ -6264,25 +6272,25 @@
         <v>104</v>
       </c>
       <c r="B105" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C105" s="29" t="n">
         <v>46094</v>
       </c>
       <c r="D105" s="28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E105" s="28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F105" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G105" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H105" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I105" s="28" t="str">
         <f aca="false">TEXT(C105,"yyyy-mm")</f>
@@ -6298,25 +6306,25 @@
         <v>105</v>
       </c>
       <c r="B106" s="28" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C106" s="29" t="n">
         <v>46094</v>
       </c>
       <c r="D106" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E106" s="28" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F106" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G106" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H106" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I106" s="28" t="str">
         <f aca="false">TEXT(C106,"yyyy-mm")</f>
@@ -6332,25 +6340,25 @@
         <v>106</v>
       </c>
       <c r="B107" s="28" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C107" s="29" t="n">
         <v>46097</v>
       </c>
       <c r="D107" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E107" s="28" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F107" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G107" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H107" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I107" s="28" t="str">
         <f aca="false">TEXT(C107,"yyyy-mm")</f>
@@ -6366,25 +6374,25 @@
         <v>107</v>
       </c>
       <c r="B108" s="28" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C108" s="29" t="n">
         <v>46097</v>
       </c>
       <c r="D108" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E108" s="28" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F108" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G108" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H108" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I108" s="28" t="str">
         <f aca="false">TEXT(C108,"yyyy-mm")</f>
@@ -6400,25 +6408,25 @@
         <v>108</v>
       </c>
       <c r="B109" s="28" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C109" s="29" t="n">
         <v>46098</v>
       </c>
       <c r="D109" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E109" s="28" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F109" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G109" s="28" t="n">
         <v>55</v>
       </c>
       <c r="H109" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I109" s="28" t="str">
         <f aca="false">TEXT(C109,"yyyy-mm")</f>
@@ -6434,25 +6442,25 @@
         <v>109</v>
       </c>
       <c r="B110" s="28" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C110" s="29" t="n">
         <v>46098</v>
       </c>
       <c r="D110" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F110" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G110" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H110" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I110" s="28" t="str">
         <f aca="false">TEXT(C110,"yyyy-mm")</f>
@@ -6468,25 +6476,25 @@
         <v>110</v>
       </c>
       <c r="B111" s="28" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C111" s="29" t="n">
         <v>46099</v>
       </c>
       <c r="D111" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E111" s="28" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F111" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G111" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H111" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I111" s="28" t="str">
         <f aca="false">TEXT(C111,"yyyy-mm")</f>
@@ -6502,25 +6510,25 @@
         <v>111</v>
       </c>
       <c r="B112" s="28" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C112" s="29" t="n">
         <v>46099</v>
       </c>
       <c r="D112" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E112" s="28" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F112" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G112" s="28" t="n">
         <v>10</v>
       </c>
       <c r="H112" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I112" s="28" t="str">
         <f aca="false">TEXT(C112,"yyyy-mm")</f>
@@ -6536,25 +6544,25 @@
         <v>112</v>
       </c>
       <c r="B113" s="28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C113" s="29" t="n">
         <v>46100</v>
       </c>
       <c r="D113" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E113" s="28" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F113" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G113" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H113" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I113" s="28" t="str">
         <f aca="false">TEXT(C113,"yyyy-mm")</f>
@@ -6570,25 +6578,25 @@
         <v>113</v>
       </c>
       <c r="B114" s="28" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C114" s="29" t="n">
         <v>46100</v>
       </c>
       <c r="D114" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E114" s="28" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F114" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G114" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H114" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I114" s="28" t="str">
         <f aca="false">TEXT(C114,"yyyy-mm")</f>
@@ -6604,25 +6612,25 @@
         <v>114</v>
       </c>
       <c r="B115" s="28" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C115" s="29" t="n">
         <v>46101</v>
       </c>
       <c r="D115" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F115" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G115" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H115" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I115" s="28" t="str">
         <f aca="false">TEXT(C115,"yyyy-mm")</f>
@@ -6638,25 +6646,25 @@
         <v>115</v>
       </c>
       <c r="B116" s="28" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C116" s="29" t="n">
         <v>46101</v>
       </c>
       <c r="D116" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E116" s="28" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F116" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G116" s="28" t="n">
         <v>50</v>
       </c>
       <c r="H116" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I116" s="28" t="str">
         <f aca="false">TEXT(C116,"yyyy-mm")</f>
@@ -6672,25 +6680,25 @@
         <v>116</v>
       </c>
       <c r="B117" s="28" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C117" s="29" t="n">
         <v>46104</v>
       </c>
       <c r="D117" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E117" s="28" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F117" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G117" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H117" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I117" s="28" t="str">
         <f aca="false">TEXT(C117,"yyyy-mm")</f>
@@ -6706,25 +6714,25 @@
         <v>117</v>
       </c>
       <c r="B118" s="28" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C118" s="29" t="n">
         <v>46104</v>
       </c>
       <c r="D118" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E118" s="28" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F118" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G118" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H118" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I118" s="28" t="str">
         <f aca="false">TEXT(C118,"yyyy-mm")</f>
@@ -6740,25 +6748,25 @@
         <v>118</v>
       </c>
       <c r="B119" s="28" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C119" s="29" t="n">
         <v>46105</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E119" s="28" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F119" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G119" s="28" t="n">
         <v>45</v>
       </c>
       <c r="H119" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I119" s="28" t="str">
         <f aca="false">TEXT(C119,"yyyy-mm")</f>
@@ -6774,25 +6782,25 @@
         <v>119</v>
       </c>
       <c r="B120" s="28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C120" s="29" t="n">
         <v>46105</v>
       </c>
       <c r="D120" s="28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E120" s="28" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F120" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G120" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H120" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I120" s="28" t="str">
         <f aca="false">TEXT(C120,"yyyy-mm")</f>
@@ -6808,25 +6816,25 @@
         <v>120</v>
       </c>
       <c r="B121" s="28" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C121" s="29" t="n">
         <v>46106</v>
       </c>
       <c r="D121" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E121" s="28" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F121" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G121" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H121" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I121" s="28" t="str">
         <f aca="false">TEXT(C121,"yyyy-mm")</f>
@@ -6842,25 +6850,25 @@
         <v>121</v>
       </c>
       <c r="B122" s="28" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C122" s="29" t="n">
         <v>46106</v>
       </c>
       <c r="D122" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E122" s="28" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F122" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G122" s="28" t="n">
         <v>10</v>
       </c>
       <c r="H122" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I122" s="28" t="str">
         <f aca="false">TEXT(C122,"yyyy-mm")</f>
@@ -6876,25 +6884,25 @@
         <v>122</v>
       </c>
       <c r="B123" s="28" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C123" s="29" t="n">
         <v>46107</v>
       </c>
       <c r="D123" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E123" s="28" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F123" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G123" s="28" t="n">
         <v>35</v>
       </c>
       <c r="H123" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I123" s="28" t="str">
         <f aca="false">TEXT(C123,"yyyy-mm")</f>
@@ -6910,25 +6918,25 @@
         <v>123</v>
       </c>
       <c r="B124" s="28" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C124" s="29" t="n">
         <v>46107</v>
       </c>
       <c r="D124" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E124" s="28" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F124" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G124" s="28" t="n">
         <v>15</v>
       </c>
       <c r="H124" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I124" s="28" t="str">
         <f aca="false">TEXT(C124,"yyyy-mm")</f>
@@ -6944,25 +6952,25 @@
         <v>124</v>
       </c>
       <c r="B125" s="28" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C125" s="29" t="n">
         <v>46108</v>
       </c>
       <c r="D125" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E125" s="28" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F125" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G125" s="28" t="n">
         <v>40</v>
       </c>
       <c r="H125" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I125" s="28" t="str">
         <f aca="false">TEXT(C125,"yyyy-mm")</f>
@@ -6978,25 +6986,25 @@
         <v>125</v>
       </c>
       <c r="B126" s="28" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C126" s="29" t="n">
         <v>46108</v>
       </c>
       <c r="D126" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E126" s="28" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F126" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G126" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H126" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I126" s="28" t="str">
         <f aca="false">TEXT(C126,"yyyy-mm")</f>
@@ -7012,25 +7020,25 @@
         <v>126</v>
       </c>
       <c r="B127" s="28" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C127" s="29" t="n">
         <v>46111</v>
       </c>
       <c r="D127" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E127" s="28" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F127" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G127" s="28" t="n">
         <v>30</v>
       </c>
       <c r="H127" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I127" s="28" t="str">
         <f aca="false">TEXT(C127,"yyyy-mm")</f>
@@ -7046,25 +7054,25 @@
         <v>127</v>
       </c>
       <c r="B128" s="28" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C128" s="29" t="n">
         <v>46111</v>
       </c>
       <c r="D128" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E128" s="28" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F128" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G128" s="28" t="n">
         <v>15</v>
       </c>
       <c r="H128" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I128" s="28" t="str">
         <f aca="false">TEXT(C128,"yyyy-mm")</f>
@@ -7080,25 +7088,25 @@
         <v>128</v>
       </c>
       <c r="B129" s="30" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C129" s="29" t="n">
         <v>46111</v>
       </c>
       <c r="D129" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E129" s="28" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F129" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G129" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H129" s="28" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="I129" s="28" t="str">
         <f aca="false">TEXT(C129,"yyyy-mm")</f>
@@ -7109,10 +7117,10 @@
         <v>14</v>
       </c>
       <c r="K129" s="31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L129" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7120,25 +7128,25 @@
         <v>129</v>
       </c>
       <c r="B130" s="30" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C130" s="29" t="n">
         <v>46112</v>
       </c>
       <c r="D130" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E130" s="28" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F130" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G130" s="28" t="n">
         <v>30</v>
       </c>
       <c r="H130" s="28" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="I130" s="28" t="str">
         <f aca="false">TEXT(C130,"yyyy-mm")</f>
@@ -7149,10 +7157,10 @@
         <v>14</v>
       </c>
       <c r="K130" s="31" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L130" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7160,25 +7168,25 @@
         <v>130</v>
       </c>
       <c r="B131" s="28" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C131" s="29" t="n">
         <v>46112</v>
       </c>
       <c r="D131" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E131" s="28" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F131" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G131" s="28" t="n">
         <v>35</v>
       </c>
       <c r="H131" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I131" s="28" t="str">
         <f aca="false">TEXT(C131,"yyyy-mm")</f>
@@ -7194,25 +7202,25 @@
         <v>131</v>
       </c>
       <c r="B132" s="28" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C132" s="29" t="n">
         <v>46112</v>
       </c>
       <c r="D132" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E132" s="28" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F132" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G132" s="28" t="n">
         <v>15</v>
       </c>
       <c r="H132" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I132" s="28" t="str">
         <f aca="false">TEXT(C132,"yyyy-mm")</f>
@@ -7228,25 +7236,25 @@
         <v>132</v>
       </c>
       <c r="B133" s="30" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C133" s="29" t="n">
         <v>46032</v>
       </c>
       <c r="D133" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E133" s="28" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F133" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G133" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H133" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I133" s="28" t="str">
         <f aca="false">TEXT(C133,"yyyy-mm")</f>
@@ -7257,10 +7265,10 @@
         <v>2</v>
       </c>
       <c r="K133" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L133" s="5" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7268,25 +7276,25 @@
         <v>133</v>
       </c>
       <c r="B134" s="30" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C134" s="29" t="n">
         <v>46045</v>
       </c>
       <c r="D134" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E134" s="28" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F134" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G134" s="28" t="n">
         <v>30</v>
       </c>
       <c r="H134" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I134" s="28" t="str">
         <f aca="false">TEXT(C134,"yyyy-mm")</f>
@@ -7297,10 +7305,10 @@
         <v>4</v>
       </c>
       <c r="K134" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L134" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7308,25 +7316,25 @@
         <v>134</v>
       </c>
       <c r="B135" s="30" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C135" s="29" t="n">
         <v>46060</v>
       </c>
       <c r="D135" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E135" s="28" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F135" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G135" s="28" t="n">
         <v>10</v>
       </c>
       <c r="H135" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I135" s="28" t="str">
         <f aca="false">TEXT(C135,"yyyy-mm")</f>
@@ -7337,10 +7345,10 @@
         <v>6</v>
       </c>
       <c r="K135" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L135" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7348,25 +7356,25 @@
         <v>135</v>
       </c>
       <c r="B136" s="30" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C136" s="29" t="n">
         <v>46073</v>
       </c>
       <c r="D136" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E136" s="28" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F136" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G136" s="28" t="n">
         <v>15</v>
       </c>
       <c r="H136" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I136" s="28" t="str">
         <f aca="false">TEXT(C136,"yyyy-mm")</f>
@@ -7377,10 +7385,10 @@
         <v>8</v>
       </c>
       <c r="K136" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L136" s="5" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7388,25 +7396,25 @@
         <v>136</v>
       </c>
       <c r="B137" s="30" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C137" s="29" t="n">
         <v>46087</v>
       </c>
       <c r="D137" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E137" s="28" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F137" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G137" s="28" t="n">
         <v>40</v>
       </c>
       <c r="H137" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I137" s="28" t="str">
         <f aca="false">TEXT(C137,"yyyy-mm")</f>
@@ -7417,10 +7425,10 @@
         <v>10</v>
       </c>
       <c r="K137" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L137" s="5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7428,25 +7436,25 @@
         <v>137</v>
       </c>
       <c r="B138" s="30" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C138" s="29" t="n">
         <v>46094</v>
       </c>
       <c r="D138" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E138" s="28" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F138" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G138" s="28" t="n">
         <v>30</v>
       </c>
       <c r="H138" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I138" s="28" t="str">
         <f aca="false">TEXT(C138,"yyyy-mm")</f>
@@ -7457,10 +7465,10 @@
         <v>11</v>
       </c>
       <c r="K138" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L138" s="5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7468,25 +7476,25 @@
         <v>138</v>
       </c>
       <c r="B139" s="30" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C139" s="29" t="n">
         <v>46039</v>
       </c>
       <c r="D139" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E139" s="28" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F139" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G139" s="28" t="n">
         <v>20</v>
       </c>
       <c r="H139" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I139" s="28" t="str">
         <f aca="false">TEXT(C139,"yyyy-mm")</f>
@@ -7497,10 +7505,10 @@
         <v>3</v>
       </c>
       <c r="K139" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L139" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7508,25 +7516,25 @@
         <v>139</v>
       </c>
       <c r="B140" s="30" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C140" s="29" t="n">
         <v>46067</v>
       </c>
       <c r="D140" s="28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E140" s="28" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F140" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G140" s="28" t="n">
         <v>15</v>
       </c>
       <c r="H140" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I140" s="28" t="str">
         <f aca="false">TEXT(C140,"yyyy-mm")</f>
@@ -7537,10 +7545,10 @@
         <v>7</v>
       </c>
       <c r="K140" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L140" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7548,25 +7556,25 @@
         <v>140</v>
       </c>
       <c r="B141" s="30" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C141" s="29" t="n">
         <v>46085</v>
       </c>
       <c r="D141" s="28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E141" s="28" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G141" s="28" t="n">
         <v>25</v>
       </c>
       <c r="H141" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I141" s="28" t="str">
         <f aca="false">TEXT(C141,"yyyy-mm")</f>
@@ -7577,10 +7585,10 @@
         <v>10</v>
       </c>
       <c r="K141" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L141" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7588,25 +7596,25 @@
         <v>141</v>
       </c>
       <c r="B142" s="30" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C142" s="29" t="n">
         <v>46102</v>
       </c>
       <c r="D142" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E142" s="28" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F142" s="28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G142" s="28" t="n">
         <v>30</v>
       </c>
       <c r="H142" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I142" s="28" t="str">
         <f aca="false">TEXT(C142,"yyyy-mm")</f>
@@ -7617,10 +7625,10 @@
         <v>12</v>
       </c>
       <c r="K142" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L142" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -7651,32 +7659,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="32" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">COUNTIFS('Tickets (raw)'!$D$3:$D$142,A4)</f>
@@ -7701,7 +7709,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">COUNTIFS('Tickets (raw)'!$D$3:$D$142,A5)</f>
@@ -7726,7 +7734,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">COUNTIFS('Tickets (raw)'!$D$3:$D$142,A6)</f>
@@ -7751,7 +7759,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">COUNTIFS('Tickets (raw)'!$D$3:$D$142,A7)</f>
@@ -7776,7 +7784,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">COUNTIFS('Tickets (raw)'!$D$3:$D$142,A8)</f>
@@ -7801,7 +7809,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">COUNTIFS('Tickets (raw)'!$D$3:$D$142,A9)</f>
@@ -7826,7 +7834,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">SUM(B4:B9)</f>
@@ -7847,21 +7855,21 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B14" s="36" t="n">
         <f aca="false">COUNTIFS('Tickets (raw)'!$I$3:$I$142,A14)</f>
@@ -7878,7 +7886,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B15" s="36" t="n">
         <f aca="false">COUNTIFS('Tickets (raw)'!$I$3:$I$142,A15)</f>
@@ -7895,7 +7903,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B16" s="36" t="n">
         <f aca="false">COUNTIFS('Tickets (raw)'!$I$3:$I$142,A16)</f>
@@ -7912,10 +7920,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="32" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8046,7 +8054,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B34" s="17" t="n">
         <f aca="false">MAX(B20:B33)</f>
@@ -8081,35 +8089,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="37" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B3" s="37" t="n">
         <v>7</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D3" s="38" t="n">
         <v>3120000</v>
@@ -8120,13 +8128,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="37" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B4" s="37" t="n">
         <v>18</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D4" s="38" t="n">
         <v>300</v>
@@ -8137,111 +8145,111 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B5" s="37" t="n">
         <v>176</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D5" s="38" t="n">
         <v>40</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="37" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B6" s="37" t="n">
         <v>188</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D6" s="38" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="37" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B7" s="37" t="n">
         <v>179</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D7" s="37"/>
       <c r="E7" s="37" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="37" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B8" s="37" t="n">
         <v>185</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D8" s="37"/>
       <c r="E8" s="37" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="37" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B9" s="37" t="n">
         <v>193</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D9" s="38" t="n">
         <v>47</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="37" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B10" s="37" t="n">
         <v>244</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D10" s="37"/>
       <c r="E10" s="37" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="37" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B11" s="37"/>
       <c r="C11" s="37" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D11" s="37"/>
       <c r="E11" s="37" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -8272,24 +8280,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8297,16 +8305,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8314,16 +8322,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8331,16 +8339,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8348,16 +8356,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8365,16 +8373,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8382,16 +8390,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8399,16 +8407,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -8439,96 +8447,96 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B3" s="41" t="n">
         <f aca="false">Summary!B27</f>
         <v>41600</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="37" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B4" s="42" t="n">
         <f aca="false">7500*4</f>
         <v>30000</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B5" s="42" t="n">
         <f aca="false">3*12*8*Summary!B24</f>
         <v>5760</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="37" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B6" s="42" t="n">
         <f aca="false">29.9*4*Summary!B24</f>
         <v>2392</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
